--- a/output/ValueSet-RNDSErros.xlsx
+++ b/output/ValueSet-RNDSErros.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-08T19:34:48-03:00</t>
+    <t>2026-10-14T15:26:34-03:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/output/ValueSet-RNDSErros.xlsx
+++ b/output/ValueSet-RNDSErros.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-14T15:26:34-03:00</t>
+    <t>2026-10-16T15:27:55-03:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/output/ValueSet-RNDSErros.xlsx
+++ b/output/ValueSet-RNDSErros.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-16T15:27:55-03:00</t>
+    <t>2026-10-16T16:14:49-03:00</t>
   </si>
   <si>
     <t>Publisher</t>
